--- a/RELATÓRIO DESPESAS REDE PARANÁ - 2026.xlsx
+++ b/RELATÓRIO DESPESAS REDE PARANÁ - 2026.xlsx
@@ -24,7 +24,6 @@
     <sheet name="14" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="15" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="ADM" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="0" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -656,8 +655,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -674,12 +673,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -688,8 +687,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -698,12 +697,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 3.414.904,28</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -712,8 +711,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -722,12 +721,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 389.553,62</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 299.226,54</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -736,8 +735,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -746,12 +745,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 1.629,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>1629</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -760,12 +757,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 416.528,22</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 370.636,86</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -774,12 +771,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>436</v>
       </c>
     </row>
@@ -790,12 +787,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 159.553,14</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 140.377,48</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -804,12 +801,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 54.453,28</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -818,12 +815,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 53.500,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -836,12 +833,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -854,10 +851,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -870,10 +867,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>238</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 51.729,62</t>
         </is>
@@ -886,10 +883,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>238</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 51.729,62</t>
         </is>
@@ -902,12 +899,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 67.684,07</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 54.472,06</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -916,8 +913,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 6.142,76</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -926,12 +927,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 1.535.187,13</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -940,8 +941,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -950,8 +951,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -960,8 +965,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -970,49 +979,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1029,8 +1038,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1047,12 +1056,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1061,8 +1070,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1071,12 +1080,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 238.983,36</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1085,8 +1094,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -1095,12 +1104,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 30.870,99</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 19.070,20</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1109,8 +1118,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1119,12 +1128,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 127,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>127</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1133,12 +1140,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 36.001,51</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 12.209,28</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1147,12 +1154,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>19</v>
       </c>
     </row>
@@ -1163,12 +1170,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 4.898,15</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 4.919,27</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1177,12 +1184,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 2.267,37</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -1191,12 +1198,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 4.300,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -1209,12 +1216,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -1227,10 +1234,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -1243,10 +1250,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 335,84</t>
         </is>
@@ -1259,10 +1266,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 335,84</t>
         </is>
@@ -1275,12 +1282,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 6.040,84</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 4.075,93</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -1289,8 +1296,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -1299,12 +1310,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 158.914,94</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -1313,8 +1324,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -1323,8 +1334,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -1333,8 +1348,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -1343,49 +1362,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1402,8 +1421,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1420,12 +1439,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1434,8 +1453,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1444,12 +1463,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 212.547,12</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1458,8 +1477,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -1468,12 +1487,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 24.913,18</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 17.097,69</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1482,8 +1501,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1492,12 +1511,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>102</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1506,12 +1523,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 27.303,48</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 6.779,34</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1520,12 +1537,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>20</v>
       </c>
     </row>
@@ -1536,12 +1553,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 4.692,49</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 5.355,89</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1550,12 +1567,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 2.643,64</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -1564,12 +1581,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.950,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -1582,12 +1599,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -1600,10 +1617,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -1616,10 +1633,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 295,83</t>
         </is>
@@ -1632,10 +1649,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 295,83</t>
         </is>
@@ -1648,12 +1665,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 5.250,24</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 3.541,92</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -1662,8 +1679,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -1672,12 +1693,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 97.859,40</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -1686,8 +1707,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -1696,8 +1717,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -1706,8 +1731,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -1716,49 +1745,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1775,8 +1804,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1793,12 +1822,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1807,8 +1836,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1817,12 +1846,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 196.999,03</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1831,8 +1860,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -1841,12 +1870,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 24.323,63</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 16.414,91</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1855,8 +1884,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1865,12 +1894,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 102,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>102</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1879,12 +1906,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 34.264,28</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 12.064,71</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1893,12 +1920,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>46</v>
       </c>
     </row>
@@ -1909,12 +1936,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 19.693,68</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 16.146,00</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1923,12 +1950,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 5.692,57</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -1937,12 +1964,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 3.650,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -1955,12 +1982,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -1973,10 +2000,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -1989,10 +2016,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>61</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 11.345,22</t>
         </is>
@@ -2005,10 +2032,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>61</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 11.345,22</t>
         </is>
@@ -2021,12 +2048,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 2.861,58</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 1.966,36</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -2035,8 +2062,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2045,12 +2076,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 107.799,87</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -2059,8 +2090,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -2069,8 +2100,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -2079,8 +2114,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -2089,49 +2128,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2148,8 +2187,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2166,12 +2205,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2180,8 +2219,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2190,12 +2229,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 189.303,84</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2204,8 +2243,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -2214,12 +2253,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 24.078,47</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 15.163,25</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2228,8 +2267,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -2238,12 +2277,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 95,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -2252,12 +2289,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 12.800,60</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 16.456,68</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -2266,12 +2303,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>37</v>
       </c>
     </row>
@@ -2282,12 +2319,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 13.930,10</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 10.833,00</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2296,12 +2333,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 4.673,28</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -2310,12 +2347,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 3.000,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -2328,12 +2365,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -2346,10 +2383,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -2362,10 +2399,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 278,44</t>
         </is>
@@ -2378,10 +2415,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 278,44</t>
         </is>
@@ -2394,12 +2431,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 1.137,92</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 934,95</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -2408,8 +2445,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2418,12 +2459,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 124.204,03</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -2432,8 +2473,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -2442,8 +2483,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -2452,8 +2497,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -2462,49 +2511,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2521,8 +2570,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2539,12 +2588,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2553,8 +2602,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2563,12 +2612,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 191.210,15</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2577,8 +2626,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -2587,12 +2636,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 24.782,99</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 15.413,92</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2601,8 +2650,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -2611,12 +2660,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 94,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>94</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -2625,12 +2672,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 21.135,36</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 13.782,53</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -2639,12 +2686,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>22</v>
       </c>
     </row>
@@ -2655,12 +2702,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 8.010,45</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 5.714,69</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2669,12 +2716,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 2.737,34</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -2683,12 +2730,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.950,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -2701,12 +2748,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -2719,10 +2766,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -2735,10 +2782,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 203,39</t>
         </is>
@@ -2751,10 +2798,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 203,39</t>
         </is>
@@ -2767,12 +2814,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 4.053,38</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 2.921,60</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -2781,8 +2828,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2791,12 +2842,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 121.908,58</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -2805,8 +2856,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -2815,8 +2866,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -2825,8 +2880,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -2835,49 +2894,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2894,8 +2953,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2912,12 +2971,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2926,8 +2985,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2936,12 +2995,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 299.110,15</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2950,8 +3009,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -2960,12 +3019,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 24.029,87</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2974,8 +3033,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -2984,12 +3043,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 137,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>137</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -2998,12 +3055,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 21.358,73</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 38.028,40</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -3012,12 +3069,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>47</v>
       </c>
     </row>
@@ -3028,12 +3085,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 16.110,58</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 15.219,53</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -3042,12 +3099,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 6.081,02</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -3056,12 +3113,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 4.850,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -3074,12 +3131,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -3092,10 +3149,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -3108,10 +3165,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 540,07</t>
         </is>
@@ -3124,10 +3181,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 540,07</t>
         </is>
@@ -3140,12 +3197,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 2.957,50</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -3154,8 +3211,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -3164,12 +3225,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -3178,8 +3239,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -3188,8 +3249,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -3198,8 +3263,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -3208,49 +3277,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3267,8 +3336,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3285,12 +3354,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -3299,8 +3368,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -3309,12 +3378,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 353.672,04</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -3323,8 +3392,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -3333,12 +3402,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 27.809,26</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -3347,8 +3416,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -3357,12 +3426,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 174,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>174</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -3371,12 +3438,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 42.712,29</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 8.285,49</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -3385,12 +3452,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>90</v>
       </c>
     </row>
@@ -3401,12 +3468,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 32.187,52</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 29.199,35</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -3415,12 +3482,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 11.387,35</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -3429,12 +3496,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 6.450,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -3447,12 +3514,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -3465,10 +3532,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -3481,10 +3548,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 695,54</t>
         </is>
@@ -3497,10 +3564,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 695,54</t>
         </is>
@@ -3513,12 +3580,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 2.555,89</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -3527,8 +3594,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -3537,12 +3608,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -3551,8 +3622,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -3561,8 +3632,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -3571,8 +3646,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -3581,49 +3660,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3635,386 +3714,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>DESPESAS DEPTO PESSOAL - 2026 GRUPO PARANÁ</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>DESCRIÇÃO</t>
-        </is>
-      </c>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Salarios</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>Bruto</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 244.394,11</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Impostos</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>Desc. Func.</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 22.680,18</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>13º Sal.</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Qtde Func.</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 55,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Rescisões</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Vale Transp.</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Pago</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Desc. Func.</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 24,80</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Refeições desc. Fun.</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 1.900,00</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Horas Extras</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>Desc.</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="n"/>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="n"/>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 781,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="n"/>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 781,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Convênio desc. Fun.</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 10.512,83</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>PM</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>Férias</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 20.081,78</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Prêmio / Meta</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>Uniformes</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Mat. Escritório</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="24" t="inlineStr">
-        <is>
-          <t>TOTAL DESPESAS</t>
-        </is>
-      </c>
-      <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="A9:B9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4030,12 +3736,12 @@
           <t>DESCRIÇÃO</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4044,8 +3750,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -4054,12 +3760,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 244.394,11</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -4068,8 +3774,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -4078,12 +3784,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 21.411,78</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -4092,8 +3798,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -4102,12 +3808,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="F10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -4116,12 +3820,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -4130,13 +3834,13 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>0</v>
+      <c r="F12" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -4146,12 +3850,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -4160,12 +3864,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 24,80</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -4174,12 +3878,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 1.900,00</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -4192,12 +3896,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -4210,10 +3914,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -4226,12 +3930,12 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
+      <c r="E18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 781,84</t>
         </is>
       </c>
     </row>
@@ -4242,12 +3946,12 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
+      <c r="E19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 781,84</t>
         </is>
       </c>
     </row>
@@ -4258,12 +3962,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 10.512,83</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -4272,8 +3976,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -4282,12 +3990,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -4296,8 +4004,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="10" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -4306,8 +4014,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -4316,8 +4028,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="14" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="14" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -4326,49 +4042,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
-    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4385,8 +4101,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4403,12 +4119,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4417,8 +4133,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -4427,12 +4143,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 312.894,44</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -4441,8 +4157,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -4451,12 +4167,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 41.822,63</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 25.243,50</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -4465,8 +4181,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -4475,12 +4191,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 148,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>148</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -4489,12 +4203,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 34.391,13</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 36.424,65</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -4503,12 +4217,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4519,12 +4233,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 3.167,45</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 3.448,44</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -4533,12 +4247,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 880,19</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -4547,12 +4261,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 4.300,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -4565,12 +4279,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -4583,10 +4297,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -4599,10 +4313,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 1.196,97</t>
         </is>
@@ -4615,10 +4329,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 1.196,97</t>
         </is>
@@ -4631,12 +4345,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 7.259,33</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 5.908,79</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -4645,8 +4359,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -4655,12 +4373,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 252.352,06</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -4669,8 +4387,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -4679,8 +4397,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -4689,8 +4411,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -4699,49 +4425,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4758,8 +4484,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4776,12 +4502,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4790,8 +4516,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -4800,12 +4526,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 140.688,26</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -4814,8 +4540,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -4824,12 +4550,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 16.229,33</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 11.607,77</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -4838,8 +4564,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -4848,12 +4574,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 64,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>64</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -4862,12 +4586,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 10.194,50</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -4876,12 +4600,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4892,12 +4616,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 1.154,63</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 1.647,66</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -4906,12 +4630,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 819,17</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -4920,12 +4644,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.100,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -4938,12 +4662,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -4956,10 +4680,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -4972,10 +4696,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 153,40</t>
         </is>
@@ -4988,10 +4712,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 153,40</t>
         </is>
@@ -5004,12 +4728,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 3.867,86</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 3.736,99</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -5018,8 +4742,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -5028,12 +4756,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 68.350,02</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -5042,8 +4770,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -5052,8 +4780,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -5062,8 +4794,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -5072,49 +4808,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5131,8 +4867,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5149,12 +4885,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -5163,8 +4899,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -5173,12 +4909,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 235.075,37</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -5187,8 +4923,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -5197,12 +4933,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 30.131,69</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 19.946,69</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -5211,8 +4947,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -5221,12 +4957,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 119,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>119</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -5235,12 +4969,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 29.510,97</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 37.753,13</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -5249,12 +4983,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>51</v>
       </c>
     </row>
@@ -5265,12 +4999,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 19.528,26</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 16.811,03</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -5279,12 +5013,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 6.304,56</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -5293,12 +5027,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 3.850,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -5311,12 +5045,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -5329,10 +5063,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -5345,10 +5079,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 15.269,83</t>
         </is>
@@ -5361,10 +5095,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>74</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 15.269,83</t>
         </is>
@@ -5377,12 +5111,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 3.712,24</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 2.820,11</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -5391,8 +5125,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -5401,12 +5139,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 131.909,08</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -5415,8 +5153,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -5425,8 +5163,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -5435,8 +5177,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -5445,49 +5191,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5504,8 +5250,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5522,12 +5268,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -5536,8 +5282,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -5546,12 +5292,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 191.856,81</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -5560,8 +5306,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -5570,12 +5316,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 25.038,17</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 16.424,81</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -5584,8 +5330,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -5594,12 +5340,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 100,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -5608,12 +5352,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 15.568,31</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 52.336,91</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -5622,12 +5366,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>34</v>
       </c>
     </row>
@@ -5638,12 +5382,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 11.067,94</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 10.734,28</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -5652,12 +5396,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 4.253,29</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -5666,12 +5410,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 3.550,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -5684,12 +5428,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -5702,10 +5446,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -5718,10 +5462,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>58</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 11.218,30</t>
         </is>
@@ -5734,10 +5478,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>58</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 11.218,30</t>
         </is>
@@ -5750,12 +5494,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 2.705,69</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 2.027,08</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -5764,8 +5508,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -5774,12 +5522,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 128.816,08</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -5788,8 +5536,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -5798,8 +5546,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -5808,8 +5560,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -5818,49 +5574,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5877,8 +5633,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5895,12 +5651,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -5909,8 +5665,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -5919,12 +5675,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 159.065,08</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -5933,8 +5689,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -5943,12 +5699,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 22.588,86</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 13.618,12</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -5957,8 +5713,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -5967,12 +5723,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 80,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -5981,12 +5735,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 18.753,16</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 48.563,04</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -5995,12 +5749,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>12</v>
       </c>
     </row>
@@ -6011,12 +5765,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 4.427,36</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 3.980,41</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -6025,12 +5779,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 1.321,60</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -6039,12 +5793,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.100,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -6057,12 +5811,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -6075,10 +5829,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -6091,10 +5845,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 8.847,73</t>
         </is>
@@ -6107,10 +5861,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>44</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 8.847,73</t>
         </is>
@@ -6123,12 +5877,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 5.524,48</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 3.615,24</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -6137,8 +5891,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -6147,12 +5905,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 114.993,99</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -6161,8 +5919,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -6171,8 +5929,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -6181,8 +5943,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -6191,49 +5957,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6250,8 +6016,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6268,12 +6034,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -6282,8 +6048,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -6292,12 +6058,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 160.043,91</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -6306,8 +6072,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -6316,12 +6082,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 18.440,39</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 12.625,13</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -6330,8 +6096,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -6340,12 +6106,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 88,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>88</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -6354,12 +6118,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 21.324,67</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 23.579,43</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -6368,12 +6132,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>20</v>
       </c>
     </row>
@@ -6384,12 +6148,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 8.508,47</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 6.745,63</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -6398,12 +6162,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 2.295,49</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -6412,12 +6176,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.550,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -6430,12 +6194,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -6448,10 +6212,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -6464,10 +6228,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 173,84</t>
         </is>
@@ -6480,10 +6244,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 173,84</t>
         </is>
@@ -6496,12 +6260,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 4.086,02</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 2.485,26</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -6510,8 +6274,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -6520,12 +6288,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 82.266,42</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -6534,8 +6302,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -6544,8 +6312,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -6554,8 +6326,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -6564,49 +6340,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6623,8 +6399,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6641,12 +6417,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -6655,8 +6431,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -6665,12 +6441,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 161.416,75</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -6679,8 +6455,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -6689,12 +6465,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 18.011,69</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 12.795,28</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -6703,8 +6479,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -6713,12 +6489,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 81,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>81</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -6727,12 +6501,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 45.379,40</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 32.844,71</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -6741,12 +6515,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -6757,12 +6531,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 2.294,86</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 2.947,28</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -6771,12 +6545,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 1.160,89</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -6785,12 +6559,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.900,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -6803,12 +6577,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -6821,10 +6595,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -6837,10 +6611,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 218,70</t>
         </is>
@@ -6853,10 +6627,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 218,70</t>
         </is>
@@ -6869,12 +6643,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 1.722,82</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 1.710,96</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -6883,8 +6657,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -6893,12 +6671,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 78.242,92</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -6907,8 +6685,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -6917,8 +6695,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -6927,8 +6709,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -6937,49 +6723,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6996,8 +6782,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7014,12 +6800,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>JAN</t>
-        </is>
-      </c>
-      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>FEV</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -7028,8 +6814,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -7038,12 +6824,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 127.643,86</t>
         </is>
       </c>
-      <c r="D6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -7052,8 +6838,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -7062,12 +6848,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 13.802,29</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 10.182,68</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -7076,8 +6862,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -7086,12 +6872,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>R$ 63,00</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -7100,12 +6884,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 39.526,98</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 25.372,91</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -7114,12 +6898,12 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="F12" s="9" t="n">
         <v>16</v>
       </c>
     </row>
@@ -7130,12 +6914,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 9.881,20</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 6.675,02</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -7144,12 +6928,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 1.910,72</t>
         </is>
       </c>
-      <c r="D14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -7158,12 +6942,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.100,00</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -7176,12 +6960,12 @@
           <t>Desc.</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>Qtde</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -7194,10 +6978,10 @@
           <t>60</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
@@ -7210,10 +6994,10 @@
           <t>100</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="F18" s="15" t="inlineStr">
         <is>
           <t>R$ 174,68</t>
         </is>
@@ -7226,10 +7010,10 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="F19" s="16" t="inlineStr">
         <is>
           <t>R$ 174,68</t>
         </is>
@@ -7242,12 +7026,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 3.435,45</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 2.700,65</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -7256,8 +7040,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -7266,12 +7054,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 47.487,96</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -7280,8 +7068,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
-      <c r="C23" s="15" t="n"/>
-      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -7290,8 +7078,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -7300,8 +7092,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -7310,49 +7106,49 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
-      <c r="C26" s="3" t="n"/>
+      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E24:F24"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="A9:B9"/>
+    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RELATÓRIO DESPESAS REDE PARANÁ - 2026.xlsx
+++ b/RELATÓRIO DESPESAS REDE PARANÁ - 2026.xlsx
@@ -655,6 +655,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -673,6 +675,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -687,6 +695,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -697,6 +707,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 3.296.746,85</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 3.414.904,28</t>
@@ -711,6 +727,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -721,6 +739,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 302.400,27</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 299.226,54</t>
@@ -735,6 +759,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -745,6 +771,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>1588</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>1629</v>
       </c>
@@ -757,6 +787,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 416.528,22</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 370.636,86</t>
@@ -771,6 +807,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>422</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -787,6 +831,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 159.553,14</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 140.377,48</t>
@@ -801,6 +851,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 51.591,70</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 54.453,28</t>
@@ -815,6 +871,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 45.990,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 53.500,00</t>
@@ -831,6 +893,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -851,6 +923,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 285,73</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -867,6 +947,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>103</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 25.189,14</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>238</v>
       </c>
@@ -883,6 +971,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>104</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 25.474,87</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>238</v>
       </c>
@@ -899,6 +995,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 50.740,74</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 54.472,06</t>
@@ -913,6 +1015,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 8.274,18</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 6.142,76</t>
@@ -927,6 +1035,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -941,6 +1055,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -951,6 +1067,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 997,20</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -965,6 +1087,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 512,70</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -979,47 +1107,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -1038,6 +1185,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1056,6 +1205,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -1070,6 +1225,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -1080,6 +1237,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 237.490,46</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 238.983,36</t>
@@ -1094,6 +1257,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -1104,6 +1269,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 19.880,25</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 19.070,20</t>
@@ -1118,6 +1289,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -1128,6 +1301,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>121</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>127</v>
       </c>
@@ -1140,6 +1317,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 36.001,51</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 12.209,28</t>
@@ -1154,6 +1337,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -1170,6 +1361,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 4.898,15</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 4.919,27</t>
@@ -1184,6 +1381,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 2.265,79</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 2.267,37</t>
@@ -1198,6 +1401,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 3.825,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 4.300,00</t>
@@ -1214,6 +1423,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -1234,6 +1453,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -1250,6 +1477,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 11.181,80</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
@@ -1266,6 +1501,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>59</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 11.181,80</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
@@ -1282,6 +1525,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 3.779,70</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 4.075,93</t>
@@ -1296,6 +1545,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -1310,6 +1565,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -1324,6 +1585,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -1334,6 +1597,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -1348,6 +1617,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -1362,47 +1637,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -1421,6 +1715,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1439,6 +1735,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -1453,6 +1755,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -1463,6 +1767,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 191.763,21</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 212.547,12</t>
@@ -1477,6 +1787,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -1487,6 +1799,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 16.192,38</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 17.097,69</t>
@@ -1501,6 +1819,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -1511,6 +1831,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>93</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>102</v>
       </c>
@@ -1523,6 +1847,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 27.303,48</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 6.779,34</t>
@@ -1537,6 +1867,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -1553,6 +1891,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 4.692,49</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 5.355,89</t>
@@ -1567,6 +1911,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 2.189,51</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 2.643,64</t>
@@ -1581,6 +1931,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 2.160,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.950,00</t>
@@ -1597,6 +1953,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -1617,6 +1983,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -1633,6 +2007,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 8.521,99</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
@@ -1649,6 +2031,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>44</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 8.521,99</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
@@ -1665,6 +2055,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 2.651,31</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 3.541,92</t>
@@ -1679,6 +2075,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -1693,6 +2095,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -1707,6 +2115,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -1717,6 +2127,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -1731,6 +2147,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -1745,47 +2167,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -1804,6 +2245,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1822,6 +2265,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -1836,6 +2285,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -1846,6 +2297,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 204.063,00</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 196.999,03</t>
@@ -1860,6 +2317,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -1870,6 +2329,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 16.004,88</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 16.414,91</t>
@@ -1884,6 +2349,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -1894,6 +2361,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>106</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>102</v>
       </c>
@@ -1906,6 +2377,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 34.264,28</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 12.064,71</t>
@@ -1920,6 +2397,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>50</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -1936,6 +2421,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 19.693,68</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 16.146,00</t>
@@ -1950,6 +2441,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 5.720,03</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 5.692,57</t>
@@ -1964,6 +2461,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 3.285,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 3.650,00</t>
@@ -1980,6 +2483,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -2000,6 +2513,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -2016,6 +2537,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 217,86</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>61</v>
       </c>
@@ -2032,6 +2561,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 217,86</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>61</v>
       </c>
@@ -2048,6 +2585,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 2.063,13</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 1.966,36</t>
@@ -2062,6 +2605,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -2076,6 +2625,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -2090,6 +2645,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -2100,6 +2657,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -2114,6 +2677,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -2128,47 +2697,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -2187,6 +2775,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2205,6 +2795,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -2219,6 +2815,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -2229,6 +2827,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 199.318,85</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 189.303,84</t>
@@ -2243,6 +2847,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -2253,6 +2859,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 16.164,49</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 15.163,25</t>
@@ -2267,6 +2879,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -2277,6 +2891,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>95</v>
       </c>
@@ -2289,6 +2907,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 12.800,60</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 16.456,68</t>
@@ -2303,6 +2927,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>33</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -2319,6 +2951,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 13.930,10</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 10.833,00</t>
@@ -2333,6 +2971,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 4.136,24</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 4.673,28</t>
@@ -2347,6 +2991,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 2.745,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 3.000,00</t>
@@ -2363,6 +3013,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -2383,6 +3043,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -2399,6 +3067,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 330,32</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
@@ -2415,6 +3091,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 330,32</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
@@ -2431,6 +3115,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 1.259,25</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 934,95</t>
@@ -2445,6 +3135,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -2459,6 +3155,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -2473,6 +3175,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -2483,6 +3187,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -2497,6 +3207,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 44,90</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -2511,47 +3227,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -2570,6 +3305,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2588,6 +3325,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -2602,6 +3345,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -2612,6 +3357,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 181.475,35</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 191.210,15</t>
@@ -2626,6 +3377,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -2636,6 +3389,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 14.516,83</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 15.413,92</t>
@@ -2650,6 +3409,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -2660,6 +3421,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>94</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>94</v>
       </c>
@@ -2672,6 +3437,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 21.135,36</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 13.782,53</t>
@@ -2686,6 +3457,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -2702,6 +3481,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 8.010,45</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 5.714,69</t>
@@ -2716,6 +3501,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 2.759,89</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 2.737,34</t>
@@ -2730,6 +3521,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 2.700,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.950,00</t>
@@ -2746,6 +3543,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -2766,6 +3573,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -2782,6 +3597,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 228,90</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
@@ -2798,6 +3621,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 228,90</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
@@ -2814,6 +3645,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 1.899,31</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 2.921,60</t>
@@ -2828,6 +3665,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -2842,6 +3685,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -2856,6 +3705,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -2866,6 +3717,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -2880,6 +3737,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -2894,47 +3757,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -2953,6 +3835,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2971,6 +3855,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -2985,6 +3875,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -2995,6 +3887,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 281.209,15</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 299.110,15</t>
@@ -3009,6 +3907,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -3019,6 +3919,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 22.396,91</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 24.029,87</t>
@@ -3033,6 +3939,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -3043,6 +3951,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>133</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>137</v>
       </c>
@@ -3055,6 +3967,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 21.358,73</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 38.028,40</t>
@@ -3069,6 +3987,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>43</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -3085,6 +4011,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 16.110,58</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 15.219,53</t>
@@ -3099,6 +4031,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 5.287,38</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 6.081,02</t>
@@ -3113,6 +4051,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 4.275,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 4.850,00</t>
@@ -3129,6 +4073,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -3149,6 +4103,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -3165,6 +4127,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 574,79</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
@@ -3181,6 +4151,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 574,79</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
@@ -3197,6 +4175,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 3.042,00</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 2.957,50</t>
@@ -3211,6 +4195,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -3225,6 +4215,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -3239,6 +4235,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -3249,6 +4247,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -3263,6 +4267,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -3277,47 +4287,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -3336,6 +4365,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3354,6 +4385,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -3368,6 +4405,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -3378,6 +4417,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 332.699,63</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 353.672,04</t>
@@ -3392,6 +4437,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -3402,6 +4449,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 25.866,34</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 27.809,26</t>
@@ -3416,6 +4469,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -3426,6 +4481,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>161</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>174</v>
       </c>
@@ -3438,6 +4497,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 42.712,29</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 8.285,49</t>
@@ -3452,6 +4517,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>83</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -3468,6 +4541,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 32.187,52</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 29.199,35</t>
@@ -3482,6 +4561,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 10.783,78</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 11.387,35</t>
@@ -3496,6 +4581,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 4.905,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 6.450,00</t>
@@ -3512,6 +4603,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -3532,6 +4633,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -3548,6 +4657,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 737,88</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
@@ -3564,6 +4681,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 737,88</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
@@ -3580,6 +4705,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 2.281,50</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 2.555,89</t>
@@ -3594,6 +4725,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -3608,6 +4745,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -3622,6 +4765,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -3632,6 +4777,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -3646,6 +4797,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -3660,47 +4817,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -3719,6 +4895,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -3736,12 +4914,19 @@
           <t>DESCRIÇÃO</t>
         </is>
       </c>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
         </is>
       </c>
-      <c r="F4" s="3" t="n"/>
+      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -3750,8 +4935,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="4" t="n"/>
       <c r="E5" s="6" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -3760,12 +4947,18 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 236.548,55</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 244.394,11</t>
         </is>
       </c>
-      <c r="F6" s="10" t="n"/>
+      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -3774,8 +4967,10 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="10" t="n"/>
       <c r="E7" s="9" t="n"/>
-      <c r="F7" s="10" t="n"/>
+      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -3784,12 +4979,18 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 20.429,18</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 21.411,78</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n"/>
+      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -3798,8 +4999,10 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="4" t="n"/>
       <c r="E9" s="6" t="n"/>
-      <c r="F9" s="4" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -3808,10 +5011,14 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="D10" s="10" t="n"/>
       <c r="E10" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="F10" s="10" t="n"/>
+      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -3820,12 +5027,18 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="F11" s="10" t="n"/>
+      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -3834,6 +5047,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -3850,12 +5071,18 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="F13" s="10" t="n"/>
+      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -3864,12 +5091,18 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 148,41</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 24,80</t>
         </is>
       </c>
-      <c r="F14" s="10" t="n"/>
+      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -3878,12 +5111,18 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 1.755,00</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 1.900,00</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n"/>
+      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -3894,6 +5133,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -3914,6 +5163,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 285,73</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -3930,6 +5187,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 54,95</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>1</v>
       </c>
@@ -3946,6 +5211,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 340,68</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>1</v>
       </c>
@@ -3962,12 +5235,18 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 9.554,92</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 10.512,83</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n"/>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -3976,12 +5255,18 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="F21" s="10" t="n"/>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -3990,12 +5275,18 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="F22" s="10" t="n"/>
+      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -4004,8 +5295,10 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="10" t="n"/>
       <c r="E23" s="15" t="n"/>
-      <c r="F23" s="10" t="n"/>
+      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -4014,12 +5307,18 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 100,10</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="F24" s="10" t="n"/>
+      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -4028,12 +5327,18 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 49,49</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="F25" s="14" t="n"/>
+      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -4042,47 +5347,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
     <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -4101,6 +5425,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -4119,6 +5445,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -4133,6 +5465,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -4143,6 +5477,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 305.444,14</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 312.894,44</t>
@@ -4157,6 +5497,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -4167,6 +5509,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 24.487,55</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 25.243,50</t>
@@ -4181,6 +5529,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -4191,6 +5541,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>149</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>148</v>
       </c>
@@ -4203,6 +5557,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 34.391,13</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 36.424,65</t>
@@ -4217,6 +5577,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -4233,6 +5601,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 3.167,45</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 3.448,44</t>
@@ -4247,6 +5621,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 1.270,96</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 880,19</t>
@@ -4261,6 +5641,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 3.825,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 4.300,00</t>
@@ -4277,6 +5663,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -4297,6 +5693,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -4313,6 +5717,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 1.075,42</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
@@ -4329,6 +5741,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 1.075,42</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
@@ -4345,6 +5765,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 4.766,26</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 5.908,79</t>
@@ -4359,6 +5785,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -4373,6 +5805,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -4387,6 +5825,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -4397,6 +5837,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 827,30</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -4411,6 +5857,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 395,86</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -4425,47 +5877,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -4484,6 +5955,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -4502,6 +5975,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -4516,6 +5995,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -4526,6 +6007,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 126.931,49</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 140.688,26</t>
@@ -4540,6 +6027,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -4550,6 +6039,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 10.292,98</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 11.607,77</t>
@@ -4564,6 +6059,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -4574,6 +6071,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>59</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>64</v>
       </c>
@@ -4586,6 +6087,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 10.194,50</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -4600,6 +6107,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -4616,6 +6131,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 1.154,63</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 1.647,66</t>
@@ -4630,6 +6151,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 646,16</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 819,17</t>
@@ -4644,6 +6171,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 1.710,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.100,00</t>
@@ -4660,6 +6193,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -4680,6 +6223,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -4696,6 +6247,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 152,46</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
@@ -4712,6 +6271,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 152,46</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
@@ -4728,6 +6295,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 3.367,04</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 3.736,99</t>
@@ -4742,6 +6315,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -4756,6 +6335,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -4770,6 +6355,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -4780,6 +6367,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -4794,6 +6387,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -4808,47 +6407,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -4867,6 +6485,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -4885,6 +6505,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -4899,6 +6525,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -4909,6 +6537,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 214.779,33</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 235.075,37</t>
@@ -4923,6 +6557,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -4933,6 +6569,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 16.925,53</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 19.946,69</t>
@@ -4947,6 +6589,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -4957,6 +6601,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>115</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>119</v>
       </c>
@@ -4969,6 +6617,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 29.510,97</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 37.753,13</t>
@@ -4983,6 +6637,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>51</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -4999,6 +6661,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 19.528,26</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 16.811,03</t>
@@ -5013,6 +6681,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 5.961,09</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 6.304,56</t>
@@ -5027,6 +6701,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 3.465,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 3.850,00</t>
@@ -5043,6 +6723,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -5063,6 +6753,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -5079,6 +6777,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 866,60</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>74</v>
       </c>
@@ -5095,6 +6801,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 866,60</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>74</v>
       </c>
@@ -5111,6 +6825,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 2.578,88</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 2.820,11</t>
@@ -5125,6 +6845,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -5139,6 +6865,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -5153,6 +6885,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -5163,6 +6897,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -5177,6 +6917,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -5191,47 +6937,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -5250,6 +7015,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -5268,6 +7035,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -5282,6 +7055,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -5292,6 +7067,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 176.855,30</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 191.856,81</t>
@@ -5306,6 +7087,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -5316,6 +7099,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 14.201,32</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 16.424,81</t>
@@ -5330,6 +7119,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -5340,6 +7131,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>94</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>100</v>
       </c>
@@ -5352,6 +7147,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 15.568,31</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 52.336,91</t>
@@ -5366,6 +7167,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>32</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -5382,6 +7191,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 11.067,94</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 10.734,28</t>
@@ -5396,6 +7211,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 3.844,15</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 4.253,29</t>
@@ -5410,6 +7231,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 2.790,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 3.550,00</t>
@@ -5426,6 +7253,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -5446,6 +7283,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -5462,6 +7307,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 217,54</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>58</v>
       </c>
@@ -5478,6 +7331,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 217,54</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>58</v>
       </c>
@@ -5494,6 +7355,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 2.012,16</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 2.027,08</t>
@@ -5508,6 +7375,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -5522,6 +7395,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -5536,6 +7415,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -5546,6 +7427,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -5560,6 +7447,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -5574,47 +7467,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -5633,6 +7545,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -5651,6 +7565,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -5665,6 +7585,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -5675,6 +7597,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 160.996,55</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 159.065,08</t>
@@ -5689,6 +7617,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -5699,6 +7629,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 12.948,28</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 13.618,12</t>
@@ -5713,6 +7649,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -5723,6 +7661,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>79</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>80</v>
       </c>
@@ -5735,6 +7677,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 18.753,16</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 48.563,04</t>
@@ -5749,6 +7697,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>9</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -5765,6 +7721,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 4.427,36</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 3.980,41</t>
@@ -5779,6 +7741,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 1.137,15</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 1.321,60</t>
@@ -5793,6 +7761,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 2.025,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.100,00</t>
@@ -5809,6 +7783,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -5829,6 +7813,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -5845,6 +7837,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 232,22</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>44</v>
       </c>
@@ -5861,6 +7861,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 232,22</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>44</v>
       </c>
@@ -5877,6 +7885,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 3.900,15</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 3.615,24</t>
@@ -5891,6 +7905,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -5905,6 +7925,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -5919,6 +7945,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -5929,6 +7957,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -5943,6 +7977,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -5957,47 +7997,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -6016,6 +8075,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -6034,6 +8095,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -6048,6 +8115,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -6058,6 +8127,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 154.291,12</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 160.043,91</t>
@@ -6072,6 +8147,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -6082,6 +8159,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 12.103,16</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 12.625,13</t>
@@ -6096,6 +8179,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -6106,6 +8191,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>84</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>88</v>
       </c>
@@ -6118,6 +8207,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 21.324,67</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 23.579,43</t>
@@ -6132,6 +8227,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -6148,6 +8251,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 8.508,47</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 6.745,63</t>
@@ -6162,6 +8271,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 2.427,32</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 2.295,49</t>
@@ -6176,6 +8291,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 2.160,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.550,00</t>
@@ -6192,6 +8313,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -6212,6 +8343,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -6228,6 +8367,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 176,45</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
@@ -6244,6 +8391,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 176,45</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
@@ -6260,6 +8415,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 2.987,32</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 2.485,26</t>
@@ -6274,6 +8435,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -6288,6 +8455,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -6302,6 +8475,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -6312,6 +8487,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -6326,6 +8507,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -6340,47 +8527,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -6399,6 +8605,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -6417,6 +8625,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -6431,6 +8645,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -6441,6 +8657,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 157.731,17</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 161.416,75</t>
@@ -6455,6 +8677,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -6465,6 +8689,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 12.373,95</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 12.795,28</t>
@@ -6479,6 +8709,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -6489,6 +8721,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>81</v>
       </c>
@@ -6501,6 +8737,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 45.379,40</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 32.844,71</t>
@@ -6515,6 +8757,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>7</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -6531,6 +8781,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 2.294,86</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 2.947,28</t>
@@ -6545,6 +8801,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 852,97</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 1.160,89</t>
@@ -6559,6 +8821,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 2.475,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.900,00</t>
@@ -6575,6 +8843,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -6595,6 +8873,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -6611,6 +8897,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 405,81</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
@@ -6627,6 +8921,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 405,81</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
@@ -6643,6 +8945,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 1.666,08</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 1.710,96</t>
@@ -6657,6 +8965,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -6671,6 +8985,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -6685,6 +9005,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -6695,6 +9017,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 69,80</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -6709,6 +9037,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 22,45</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -6723,47 +9057,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
@@ -6782,6 +9135,8 @@
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
@@ -6800,6 +9155,12 @@
         </is>
       </c>
       <c r="B4" s="25" t="n"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>JAN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>FEV</t>
@@ -6814,6 +9175,8 @@
         </is>
       </c>
       <c r="B5" s="5" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="5" t="n"/>
       <c r="E5" s="6" t="n"/>
       <c r="F5" s="5" t="n"/>
     </row>
@@ -6824,6 +9187,12 @@
         </is>
       </c>
       <c r="B6" s="8" t="n"/>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R$ 135.149,55</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <t>R$ 127.643,86</t>
@@ -6838,6 +9207,8 @@
         </is>
       </c>
       <c r="B7" s="8" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="8" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="8" t="n"/>
     </row>
@@ -6848,6 +9219,12 @@
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>R$ 10.577,24</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
           <t>R$ 10.182,68</t>
@@ -6862,6 +9239,8 @@
         </is>
       </c>
       <c r="B9" s="5" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="5" t="n"/>
       <c r="E9" s="6" t="n"/>
       <c r="F9" s="5" t="n"/>
     </row>
@@ -6872,6 +9251,10 @@
         </is>
       </c>
       <c r="B10" s="8" t="n"/>
+      <c r="C10" s="15" t="n">
+        <v>68</v>
+      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="15" t="n">
         <v>63</v>
       </c>
@@ -6884,6 +9267,12 @@
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>R$ 39.526,98</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
       <c r="E11" s="15" t="inlineStr">
         <is>
           <t>R$ 25.372,91</t>
@@ -6898,6 +9287,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n"/>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Qtde</t>
@@ -6914,6 +9311,12 @@
         </is>
       </c>
       <c r="B13" s="8" t="n"/>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>R$ 9.881,20</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
       <c r="E13" s="9" t="inlineStr">
         <is>
           <t>R$ 6.675,02</t>
@@ -6928,6 +9331,12 @@
         </is>
       </c>
       <c r="B14" s="8" t="n"/>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>R$ 2.160,87</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>R$ 1.910,72</t>
@@ -6942,6 +9351,12 @@
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>R$ 1.890,00</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n"/>
       <c r="E15" s="16" t="inlineStr">
         <is>
           <t>R$ 2.100,00</t>
@@ -6958,6 +9373,16 @@
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Desc.</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>Qtde</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E16" s="19" t="inlineStr">
@@ -6978,6 +9403,14 @@
           <t>60</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
@@ -6994,6 +9427,14 @@
           <t>100</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>R$ 214,15</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
@@ -7010,6 +9451,14 @@
           <t>TOTAL</t>
         </is>
       </c>
+      <c r="C19" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>R$ 214,15</t>
+        </is>
+      </c>
       <c r="E19" s="13" t="n">
         <v>0</v>
       </c>
@@ -7026,6 +9475,12 @@
         </is>
       </c>
       <c r="B20" s="5" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R$ 2.931,73</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>R$ 2.700,65</t>
@@ -7040,6 +9495,12 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
       <c r="E21" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -7054,6 +9515,12 @@
         </is>
       </c>
       <c r="B22" s="8" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
       <c r="E22" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -7068,6 +9535,8 @@
         </is>
       </c>
       <c r="B23" s="8" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="8" t="n"/>
       <c r="E23" s="15" t="n"/>
       <c r="F23" s="8" t="n"/>
     </row>
@@ -7078,6 +9547,12 @@
         </is>
       </c>
       <c r="B24" s="8" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
       <c r="E24" s="15" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -7092,6 +9567,12 @@
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n"/>
       <c r="E25" s="16" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
@@ -7106,47 +9587,66 @@
         </is>
       </c>
       <c r="B26" s="25" t="n"/>
+      <c r="C26" s="3" t="n"/>
       <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="57">
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="E24:F24"/>
+    <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E23:F23"/>
+    <mergeCell ref="C14:D14"/>
     <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C20:D20"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="E13:F13"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="E6:F6"/>
+    <mergeCell ref="C21:D21"/>
     <mergeCell ref="E15:F15"/>
+    <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C8:D8"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>

--- a/RELATÓRIO DESPESAS REDE PARANÁ - 2026.xlsx
+++ b/RELATÓRIO DESPESAS REDE PARANÁ - 2026.xlsx
@@ -657,8 +657,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -681,12 +679,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -697,8 +689,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -713,12 +703,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 3.414.904,28</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -729,8 +713,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -745,12 +727,6 @@
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 299.226,54</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -761,8 +737,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -775,10 +749,6 @@
         <v>1588</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>1629</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -793,12 +763,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 370.636,86</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -815,14 +779,6 @@
       <c r="D12" s="9" t="n">
         <v>422</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>436</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -837,12 +793,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 140.377,48</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -857,12 +807,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 54.453,28</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -877,12 +821,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 53.500,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -901,16 +839,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -931,14 +859,6 @@
           <t>R$ 285,73</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -955,14 +875,6 @@
           <t>R$ 25.189,14</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>238</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 51.729,62</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -979,14 +891,6 @@
           <t>R$ 25.474,87</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>238</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 51.729,62</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -997,16 +901,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 50.740,74</t>
+          <t>R$ 59.014,92</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 54.472,06</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -1015,18 +913,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 8.274,18</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 6.142,76</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -1037,16 +925,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 510.447,12</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -1057,8 +939,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -1073,12 +953,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -1093,12 +967,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -1108,52 +976,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -1161,14 +1014,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1187,8 +1036,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1211,12 +1058,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1227,8 +1068,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1243,12 +1082,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 238.983,36</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1259,8 +1092,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -1271,16 +1102,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 19.880,25</t>
+          <t>R$ 23.246,05</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 19.070,20</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1291,8 +1116,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1305,10 +1128,6 @@
         <v>121</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>127</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1323,12 +1142,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 12.209,28</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1345,14 +1158,6 @@
       <c r="D12" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>19</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1367,12 +1172,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 4.919,27</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1387,12 +1186,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 2.267,37</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -1407,12 +1200,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 4.300,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -1431,16 +1218,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -1461,14 +1238,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -1485,14 +1254,6 @@
           <t>R$ 11.181,80</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 335,84</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -1509,14 +1270,6 @@
           <t>R$ 11.181,80</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 335,84</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1527,16 +1280,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 3.779,70</t>
+          <t>R$ 4.120,69</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 4.075,93</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -1545,18 +1292,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -1567,16 +1304,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 45.111,50</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -1587,8 +1318,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -1603,12 +1332,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -1623,12 +1346,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -1638,52 +1355,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -1691,14 +1393,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1717,8 +1415,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1741,12 +1437,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1757,8 +1447,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1773,12 +1461,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 212.547,12</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -1789,8 +1471,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -1801,16 +1481,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 16.192,38</t>
+          <t>R$ 18.444,87</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 17.097,69</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1821,8 +1495,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -1835,10 +1507,6 @@
         <v>93</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>102</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1853,12 +1521,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 6.779,34</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -1875,14 +1537,6 @@
       <c r="D12" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -1897,12 +1551,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 5.355,89</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -1917,12 +1565,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 2.643,64</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -1937,12 +1579,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 2.950,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -1961,16 +1597,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -1991,14 +1617,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -2015,14 +1633,6 @@
           <t>R$ 8.521,99</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 295,83</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -2039,14 +1649,6 @@
           <t>R$ 8.521,99</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 295,83</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2057,16 +1659,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 2.651,31</t>
+          <t>R$ 3.274,41</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 3.541,92</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -2075,18 +1671,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2097,16 +1683,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 27.532,59</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -2117,8 +1697,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -2133,12 +1711,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -2153,12 +1725,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -2168,52 +1734,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -2221,14 +1772,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2247,8 +1794,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2271,12 +1816,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2287,8 +1826,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2303,12 +1840,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 196.999,03</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2319,8 +1850,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -2331,16 +1860,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 16.004,88</t>
+          <t>R$ 19.566,98</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 16.414,91</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2351,8 +1874,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -2365,10 +1886,6 @@
         <v>106</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>102</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -2383,12 +1900,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 12.064,71</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -2405,14 +1916,6 @@
       <c r="D12" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>46</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2427,12 +1930,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 16.146,00</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2447,12 +1944,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 5.692,57</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -2467,12 +1958,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 3.650,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -2491,16 +1976,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -2521,14 +1996,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -2545,14 +2012,6 @@
           <t>R$ 217,86</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>61</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 11.345,22</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -2569,14 +2028,6 @@
           <t>R$ 217,86</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>61</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 11.345,22</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2587,16 +2038,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 2.063,13</t>
+          <t>R$ 2.433,11</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 1.966,36</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -2605,18 +2050,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -2627,16 +2062,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 46.975,92</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -2647,8 +2076,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -2663,12 +2090,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -2683,12 +2104,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -2698,52 +2113,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -2751,14 +2151,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2777,8 +2173,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2801,12 +2195,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2817,8 +2205,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -2833,12 +2219,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 189.303,84</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -2849,8 +2229,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -2861,16 +2239,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 16.164,49</t>
+          <t>R$ 18.474,12</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 15.163,25</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2881,8 +2253,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -2895,10 +2265,6 @@
         <v>97</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>95</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -2913,12 +2279,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 16.456,68</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -2935,14 +2295,6 @@
       <c r="D12" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>37</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -2957,12 +2309,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 10.833,00</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2977,12 +2323,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 4.673,28</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -2997,12 +2337,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 3.000,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -3021,16 +2355,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -3051,14 +2375,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -3075,14 +2391,6 @@
           <t>R$ 330,32</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 278,44</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -3099,14 +2407,6 @@
           <t>R$ 330,32</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 278,44</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3117,16 +2417,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 1.259,25</t>
+          <t>R$ 1.434,42</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 934,95</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -3135,18 +2429,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -3157,16 +2441,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 31.733,24</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -3177,8 +2455,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -3193,12 +2469,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -3213,12 +2483,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -3228,52 +2492,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -3281,14 +2530,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3307,8 +2552,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3331,12 +2574,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -3347,8 +2584,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -3363,12 +2598,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 191.210,15</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -3379,8 +2608,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -3391,16 +2618,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 14.516,83</t>
+          <t>R$ 18.682,01</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 15.413,92</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -3411,8 +2632,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -3425,10 +2644,6 @@
         <v>94</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>94</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -3443,12 +2658,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 13.782,53</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -3465,14 +2674,6 @@
       <c r="D12" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>22</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -3487,12 +2688,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 5.714,69</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -3507,12 +2702,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 2.737,34</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -3527,12 +2716,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 2.950,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -3551,16 +2734,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -3581,14 +2754,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -3605,14 +2770,6 @@
           <t>R$ 228,90</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 203,39</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -3629,14 +2786,6 @@
           <t>R$ 228,90</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 203,39</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3647,16 +2796,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 1.899,31</t>
+          <t>R$ 2.897,51</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 2.921,60</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -3665,18 +2808,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -3687,16 +2820,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 55.323,45</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -3707,8 +2834,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -3723,12 +2848,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -3743,12 +2862,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -3758,52 +2871,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -3811,14 +2909,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3837,8 +2931,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3861,12 +2953,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -3877,8 +2963,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -3893,12 +2977,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 299.110,15</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -3909,8 +2987,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -3925,12 +3001,6 @@
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 24.029,87</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -3941,8 +3011,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -3955,10 +3023,6 @@
         <v>133</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>137</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -3973,12 +3037,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 38.028,40</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -3995,14 +3053,6 @@
       <c r="D12" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>47</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -4017,12 +3067,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 15.219,53</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -4037,12 +3081,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 6.081,02</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -4057,12 +3095,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 4.850,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -4081,16 +3113,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -4111,14 +3133,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -4135,14 +3149,6 @@
           <t>R$ 574,79</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 540,07</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -4159,14 +3165,6 @@
           <t>R$ 574,79</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 540,07</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -4181,12 +3179,6 @@
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 2.957,50</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -4195,18 +3187,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -4221,12 +3203,6 @@
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -4237,8 +3213,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -4253,12 +3227,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -4273,12 +3241,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -4288,52 +3250,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -4341,14 +3288,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4367,8 +3310,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4391,12 +3332,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4407,8 +3342,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -4423,12 +3356,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 353.672,04</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -4439,8 +3366,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -4455,12 +3380,6 @@
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 27.809,26</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -4471,8 +3390,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -4485,10 +3402,6 @@
         <v>161</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>174</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -4503,12 +3416,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 8.285,49</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -4525,14 +3432,6 @@
       <c r="D12" s="9" t="n">
         <v>83</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>90</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -4547,12 +3446,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 29.199,35</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -4567,12 +3460,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 11.387,35</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -4587,12 +3474,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 6.450,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -4611,16 +3492,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -4641,14 +3512,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -4665,14 +3528,6 @@
           <t>R$ 737,88</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 695,54</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -4689,14 +3544,6 @@
           <t>R$ 737,88</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 695,54</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -4711,12 +3558,6 @@
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 2.555,89</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -4725,18 +3566,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -4751,12 +3582,6 @@
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -4767,8 +3592,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -4783,12 +3606,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -4803,12 +3620,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -4818,52 +3629,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -4871,14 +3667,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4897,8 +3689,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4914,19 +3704,12 @@
           <t>DESCRIÇÃO</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>JAN</t>
         </is>
       </c>
       <c r="D4" s="3" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4937,8 +3720,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="4" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -4953,12 +3734,6 @@
         </is>
       </c>
       <c r="D6" s="10" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 244.394,11</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -4969,8 +3744,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="10" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -4981,16 +3754,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 20.429,18</t>
+          <t>R$ 24.581,46</t>
         </is>
       </c>
       <c r="D8" s="14" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 21.411,78</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -5001,8 +3768,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="4" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -5015,10 +3780,6 @@
         <v>55</v>
       </c>
       <c r="D10" s="10" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>55</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -5033,12 +3794,6 @@
         </is>
       </c>
       <c r="D11" s="10" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -5055,14 +3810,6 @@
       <c r="D12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -5077,12 +3824,6 @@
         </is>
       </c>
       <c r="D13" s="10" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -5097,12 +3838,6 @@
         </is>
       </c>
       <c r="D14" s="10" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 24,80</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -5117,12 +3852,6 @@
         </is>
       </c>
       <c r="D15" s="14" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 1.900,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -5141,16 +3870,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -5171,14 +3890,6 @@
           <t>R$ 285,73</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -5195,14 +3906,6 @@
           <t>R$ 54,95</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 781,84</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -5219,14 +3922,6 @@
           <t>R$ 340,68</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 781,84</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -5237,16 +3932,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 9.554,92</t>
+          <t>R$ 11.692,85</t>
         </is>
       </c>
       <c r="D20" s="4" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 10.512,83</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -5255,18 +3944,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="10" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -5277,16 +3956,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 66.374,22</t>
         </is>
       </c>
       <c r="D22" s="10" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -5297,8 +3970,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="10" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -5313,12 +3984,6 @@
         </is>
       </c>
       <c r="D24" s="10" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -5333,12 +3998,6 @@
         </is>
       </c>
       <c r="D25" s="14" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -5348,52 +4007,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -5401,14 +4045,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5427,8 +4067,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5451,12 +4089,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -5467,8 +4099,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -5483,12 +4113,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 312.894,44</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -5499,8 +4123,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -5511,16 +4133,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 24.487,55</t>
+          <t>R$ 28.900,94</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 25.243,50</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -5531,8 +4147,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -5545,10 +4159,6 @@
         <v>149</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>148</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -5563,12 +4173,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 36.424,65</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -5585,14 +4189,6 @@
       <c r="D12" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -5607,12 +4203,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 3.448,44</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -5627,12 +4217,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 880,19</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -5647,12 +4231,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 4.300,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -5671,16 +4249,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -5701,14 +4269,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -5725,14 +4285,6 @@
           <t>R$ 1.075,42</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 1.196,97</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -5749,14 +4301,6 @@
           <t>R$ 1.075,42</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 1.196,97</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -5767,16 +4311,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 4.766,26</t>
+          <t>R$ 6.224,55</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 5.908,79</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -5785,18 +4323,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -5807,16 +4335,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 63.401,38</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -5827,8 +4349,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -5843,12 +4363,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -5863,12 +4377,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -5878,52 +4386,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -5931,14 +4424,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5957,8 +4446,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5981,12 +4468,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -5997,8 +4478,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -6013,12 +4492,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 140.688,26</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -6029,8 +4502,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -6041,16 +4512,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 10.292,98</t>
+          <t>R$ 11.594,66</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 11.607,77</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -6061,8 +4526,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -6075,10 +4538,6 @@
         <v>59</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>64</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -6093,12 +4552,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -6115,14 +4568,6 @@
       <c r="D12" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -6137,12 +4582,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 1.647,66</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -6157,12 +4596,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 819,17</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -6177,12 +4610,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 2.100,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -6201,16 +4628,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -6231,14 +4648,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -6255,14 +4664,6 @@
           <t>R$ 152,46</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 153,40</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -6279,14 +4680,6 @@
           <t>R$ 152,46</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 153,40</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -6297,16 +4690,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 3.367,04</t>
+          <t>R$ 3.926,31</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 3.736,99</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -6315,18 +4702,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -6337,16 +4714,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 21.273,47</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -6357,8 +4728,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -6373,12 +4742,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -6393,12 +4756,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -6408,52 +4765,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -6461,14 +4803,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6487,8 +4825,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6511,12 +4847,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -6527,8 +4857,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -6543,12 +4871,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 235.075,37</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -6559,8 +4881,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -6571,16 +4891,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 16.925,53</t>
+          <t>R$ 20.802,38</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 19.946,69</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -6591,8 +4905,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -6605,10 +4917,6 @@
         <v>115</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>119</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -6623,12 +4931,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 37.753,13</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -6645,14 +4947,6 @@
       <c r="D12" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>51</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -6667,12 +4961,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 16.811,03</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -6687,12 +4975,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 6.304,56</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -6707,12 +4989,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 3.850,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -6731,16 +5007,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -6761,14 +5027,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -6785,14 +5043,6 @@
           <t>R$ 866,60</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>74</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 15.269,83</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -6809,14 +5059,6 @@
           <t>R$ 866,60</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>74</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 15.269,83</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -6827,16 +5069,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 2.578,88</t>
+          <t>R$ 2.973,38</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 2.820,11</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -6845,18 +5081,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -6867,16 +5093,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 48.211,10</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -6887,8 +5107,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -6903,12 +5121,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -6923,12 +5135,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -6938,52 +5144,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -6991,14 +5182,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7017,8 +5204,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7041,12 +5226,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -7057,8 +5236,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -7073,12 +5250,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 191.856,81</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -7089,8 +5260,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -7101,16 +5270,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 14.201,32</t>
+          <t>R$ 16.557,52</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 16.424,81</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -7121,8 +5284,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -7135,10 +5296,6 @@
         <v>94</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -7153,12 +5310,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 52.336,91</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -7175,14 +5326,6 @@
       <c r="D12" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>34</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -7197,12 +5340,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 10.734,28</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -7217,12 +5354,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 4.253,29</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -7237,12 +5368,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 3.550,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -7261,16 +5386,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -7291,14 +5406,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -7315,14 +5422,6 @@
           <t>R$ 217,54</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 11.218,30</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -7339,14 +5438,6 @@
           <t>R$ 217,54</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>58</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 11.218,30</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -7357,16 +5448,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 2.012,16</t>
+          <t>R$ 2.304,08</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 2.027,08</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -7375,18 +5460,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -7397,16 +5472,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 33.226,91</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -7417,8 +5486,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -7433,12 +5500,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -7453,12 +5514,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -7468,52 +5523,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -7521,14 +5561,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7547,8 +5583,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7571,12 +5605,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -7587,8 +5615,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -7603,12 +5629,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 159.065,08</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -7619,8 +5639,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -7631,16 +5649,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 12.948,28</t>
+          <t>R$ 14.721,16</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 13.618,12</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -7651,8 +5663,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -7665,10 +5675,6 @@
         <v>79</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>80</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -7683,12 +5689,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 48.563,04</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -7705,14 +5705,6 @@
       <c r="D12" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>12</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -7727,12 +5719,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 3.980,41</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -7747,12 +5733,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 1.321,60</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -7767,12 +5747,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 2.100,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -7791,16 +5765,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -7821,14 +5785,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -7845,14 +5801,6 @@
           <t>R$ 232,22</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 8.847,73</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -7869,14 +5817,6 @@
           <t>R$ 232,22</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>44</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 8.847,73</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -7887,16 +5827,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 3.900,15</t>
+          <t>R$ 4.338,03</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 3.615,24</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -7905,18 +5839,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -7927,16 +5851,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 22.769,42</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -7947,8 +5865,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -7963,12 +5879,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -7983,12 +5893,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -7998,52 +5902,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -8051,14 +5940,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8077,8 +5962,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8101,12 +5984,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -8117,8 +5994,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -8133,12 +6008,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 160.043,91</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -8149,8 +6018,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -8161,16 +6028,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 12.103,16</t>
+          <t>R$ 14.118,06</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 12.625,13</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -8181,8 +6042,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -8195,10 +6054,6 @@
         <v>84</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>88</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -8213,12 +6068,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 23.579,43</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -8235,14 +6084,6 @@
       <c r="D12" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -8257,12 +6098,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 6.745,63</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -8277,12 +6112,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 2.295,49</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -8297,12 +6126,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 2.550,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -8321,16 +6144,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -8351,14 +6164,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -8375,14 +6180,6 @@
           <t>R$ 176,45</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 173,84</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -8399,14 +6196,6 @@
           <t>R$ 176,45</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 173,84</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -8417,16 +6206,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 2.987,32</t>
+          <t>R$ 3.469,36</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 2.485,26</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -8435,18 +6218,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -8457,16 +6230,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 27.410,20</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -8477,8 +6244,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -8493,12 +6258,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -8513,12 +6272,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -8528,52 +6281,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -8581,14 +6319,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8607,8 +6341,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8631,12 +6363,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -8647,8 +6373,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -8663,12 +6387,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 161.416,75</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -8679,8 +6397,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -8691,16 +6407,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 12.373,95</t>
+          <t>R$ 13.405,92</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 12.795,28</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -8711,8 +6421,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -8725,10 +6433,6 @@
         <v>80</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>81</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -8743,12 +6447,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 32.844,71</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -8765,14 +6463,6 @@
       <c r="D12" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>9</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -8787,12 +6477,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 2.947,28</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -8807,12 +6491,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 1.160,89</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -8827,12 +6505,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 2.900,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -8851,16 +6523,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -8881,14 +6543,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -8905,14 +6559,6 @@
           <t>R$ 405,81</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 218,70</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -8929,14 +6575,6 @@
           <t>R$ 405,81</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 218,70</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -8947,16 +6585,10 @@
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>R$ 1.666,08</t>
+          <t>R$ 1.670,99</t>
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 1.710,96</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -8965,18 +6597,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -8987,16 +6609,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 15.333,87</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -9007,8 +6623,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -9023,12 +6637,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -9043,12 +6651,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -9058,52 +6660,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -9111,14 +6698,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9137,8 +6720,6 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9161,12 +6742,6 @@
         </is>
       </c>
       <c r="D4" s="25" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>FEV</t>
-        </is>
-      </c>
-      <c r="F4" s="25" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -9177,8 +6752,6 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="5" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -9193,12 +6766,6 @@
         </is>
       </c>
       <c r="D6" s="8" t="n"/>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>R$ 127.643,86</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -9209,8 +6776,6 @@
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="8" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -9221,16 +6786,10 @@
       <c r="B8" s="12" t="n"/>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>R$ 10.577,24</t>
+          <t>R$ 11.040,89</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>R$ 10.182,68</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -9241,8 +6800,6 @@
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="5" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
@@ -9255,10 +6812,6 @@
         <v>68</v>
       </c>
       <c r="D10" s="8" t="n"/>
-      <c r="E10" s="15" t="n">
-        <v>63</v>
-      </c>
-      <c r="F10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -9273,12 +6826,6 @@
         </is>
       </c>
       <c r="D11" s="8" t="n"/>
-      <c r="E11" s="15" t="inlineStr">
-        <is>
-          <t>R$ 25.372,91</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -9295,14 +6842,6 @@
       <c r="D12" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>16</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -9317,12 +6856,6 @@
         </is>
       </c>
       <c r="D13" s="8" t="n"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>R$ 6.675,02</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -9337,12 +6870,6 @@
         </is>
       </c>
       <c r="D14" s="8" t="n"/>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>R$ 1.910,72</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -9357,12 +6884,6 @@
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>R$ 2.100,00</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
@@ -9381,16 +6902,6 @@
         </is>
       </c>
       <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>Qtde</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -9411,14 +6922,6 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n"/>
@@ -9435,14 +6938,6 @@
           <t>R$ 214,15</t>
         </is>
       </c>
-      <c r="E18" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>R$ 174,68</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="22" t="n"/>
@@ -9459,14 +6954,6 @@
           <t>R$ 214,15</t>
         </is>
       </c>
-      <c r="E19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>R$ 174,68</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -9481,12 +6968,6 @@
         </is>
       </c>
       <c r="D20" s="5" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>R$ 2.700,65</t>
-        </is>
-      </c>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -9495,18 +6976,8 @@
         </is>
       </c>
       <c r="B21" s="8" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
+      <c r="C21" s="15" t="n"/>
       <c r="D21" s="8" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -9517,16 +6988,10 @@
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 5.769,85</t>
         </is>
       </c>
       <c r="D22" s="8" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -9537,8 +7002,6 @@
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="15" t="n"/>
       <c r="D23" s="8" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
@@ -9553,12 +7016,6 @@
         </is>
       </c>
       <c r="D24" s="8" t="n"/>
-      <c r="E24" s="15" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -9573,12 +7030,6 @@
         </is>
       </c>
       <c r="D25" s="12" t="n"/>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="F25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="24" t="inlineStr">
@@ -9588,52 +7039,37 @@
       </c>
       <c r="B26" s="25" t="n"/>
       <c r="C26" s="3" t="n"/>
-      <c r="E26" s="3" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
+  <mergeCells count="39">
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C24:D24"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="E24:F24"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A16:A19"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="E10:F10"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="E6:F6"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E15:F15"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E26:F26"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="A22:B22"/>
@@ -9641,14 +7077,10 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="E22:F22"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
